--- a/resampling/input/accessibility_reports_returned/ACF_accessibility_report.xlsx
+++ b/resampling/input/accessibility_reports_returned/ACF_accessibility_report.xlsx
@@ -221,8 +221,8 @@
 </file>
 
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="2" name="ClusterAccessibility" displayName="ClusterAccessibility" ref="A1:M108" headerRowCount="1">
-  <autoFilter ref="A1:M108"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="2" name="ClusterAccessibility" displayName="ClusterAccessibility" ref="A1:M144" headerRowCount="1">
+  <autoFilter ref="A1:M144"/>
   <tableColumns count="13">
     <tableColumn id="1" name="State"/>
     <tableColumn id="2" name="LGA"/>
@@ -4829,7 +4829,6 @@
           <t>No</t>
         </is>
       </c>
-      <c r="F100" t="inlineStr"/>
       <c r="G100" t="inlineStr">
         <is>
           <t>Newly added 2026-09-20 - this ward is Stage-1-eligible for your coverage but had never had a cluster drawn in it by chance, so it was missing from your assignment list until now (a gap found and fixed today, see the accompanying email). Please review and report on it like any other row.</t>
@@ -4907,7 +4906,6 @@
           <t>No</t>
         </is>
       </c>
-      <c r="F102" t="inlineStr"/>
       <c r="G102" t="inlineStr">
         <is>
           <t>Newly added 2026-09-20 - this ward is Stage-1-eligible for your coverage but had never had a cluster drawn in it by chance, so it was missing from your assignment list until now (a gap found and fixed today, see the accompanying email). Please review and report on it like any other row.</t>
@@ -5026,7 +5024,6 @@
           <t>No</t>
         </is>
       </c>
-      <c r="F105" t="inlineStr"/>
       <c r="G105" t="inlineStr">
         <is>
           <t>Newly added 2026-09-20 - this ward is Stage-1-eligible for your coverage but had never had a cluster drawn in it by chance, so it was missing from your assignment list until now (a gap found and fixed today, see the accompanying email). Please review and report on it like any other row.</t>
@@ -5104,7 +5101,6 @@
           <t>No</t>
         </is>
       </c>
-      <c r="F107" t="inlineStr"/>
       <c r="G107" t="inlineStr">
         <is>
           <t>Newly added 2026-09-20 - this ward is Stage-1-eligible for your coverage but had never had a cluster drawn in it by chance, so it was missing from your assignment list until now (a gap found and fixed today, see the accompanying email). Please review and report on it like any other row.</t>
@@ -5305,7 +5301,6 @@
           <t>No</t>
         </is>
       </c>
-      <c r="F112" t="inlineStr"/>
       <c r="G112" t="inlineStr">
         <is>
           <t>Newly added 2026-09-20 - this ward is Stage-1-eligible for your coverage but had never had a cluster drawn in it by chance, so it was missing from your assignment list until now (a gap found and fixed today, see the accompanying email). Please review and report on it like any other row.</t>
@@ -5342,7 +5337,6 @@
           <t>No</t>
         </is>
       </c>
-      <c r="F113" t="inlineStr"/>
       <c r="G113" t="inlineStr">
         <is>
           <t>Newly added 2026-09-20 - this ward is Stage-1-eligible for your coverage but had never had a cluster drawn in it by chance, so it was missing from your assignment list until now (a gap found and fixed today, see the accompanying email). Please review and report on it like any other row.</t>
@@ -5543,7 +5537,6 @@
           <t>No</t>
         </is>
       </c>
-      <c r="F118" t="inlineStr"/>
       <c r="G118" t="inlineStr">
         <is>
           <t>Newly added 2026-09-20 - this ward is Stage-1-eligible for your coverage but had never had a cluster drawn in it by chance, so it was missing from your assignment list until now (a gap found and fixed today, see the accompanying email). Please review and report on it like any other row.</t>
@@ -5621,7 +5614,6 @@
           <t>No</t>
         </is>
       </c>
-      <c r="F120" t="inlineStr"/>
       <c r="G120" t="inlineStr">
         <is>
           <t>Newly added 2026-09-20 - this ward is Stage-1-eligible for your coverage but had never had a cluster drawn in it by chance, so it was missing from your assignment list until now (a gap found and fixed today, see the accompanying email). Please review and report on it like any other row.</t>
@@ -5822,7 +5814,6 @@
           <t>No</t>
         </is>
       </c>
-      <c r="F125" t="inlineStr"/>
       <c r="G125" t="inlineStr">
         <is>
           <t>Newly added 2026-09-20 - this ward is Stage-1-eligible for your coverage but had never had a cluster drawn in it by chance, so it was missing from your assignment list until now (a gap found and fixed today, see the accompanying email). Please review and report on it like any other row.</t>
@@ -5982,7 +5973,6 @@
           <t>No</t>
         </is>
       </c>
-      <c r="F129" t="inlineStr"/>
       <c r="G129" t="inlineStr">
         <is>
           <t>Newly added 2026-09-20 - this ward is Stage-1-eligible for your coverage but had never had a cluster drawn in it by chance, so it was missing from your assignment list until now (a gap found and fixed today, see the accompanying email). Please review and report on it like any other row.</t>
@@ -6105,7 +6095,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M108"/>
+  <dimension ref="A1:M144"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="14.4"/>
   <cols>
     <col width="14" customWidth="1" style="11" min="1" max="2"/>
@@ -11076,12 +11066,1436 @@
         </is>
       </c>
     </row>
+    <row r="109">
+      <c r="A109" t="inlineStr">
+        <is>
+          <t>Sokoto</t>
+        </is>
+      </c>
+      <c r="B109" t="inlineStr">
+        <is>
+          <t>Bodinga</t>
+        </is>
+      </c>
+      <c r="C109" t="inlineStr">
+        <is>
+          <t>Kaura Miyo</t>
+        </is>
+      </c>
+      <c r="D109" t="inlineStr">
+        <is>
+          <t>Non-IDP</t>
+        </is>
+      </c>
+      <c r="E109" t="inlineStr">
+        <is>
+          <t>non_idp_NG034002_supp2</t>
+        </is>
+      </c>
+      <c r="F109" t="inlineStr"/>
+      <c r="G109" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="H109" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" t="inlineStr">
+        <is>
+          <t>Sokoto</t>
+        </is>
+      </c>
+      <c r="B110" t="inlineStr">
+        <is>
+          <t>Bodinga</t>
+        </is>
+      </c>
+      <c r="C110" t="inlineStr">
+        <is>
+          <t>Kaura Miyo</t>
+        </is>
+      </c>
+      <c r="D110" t="inlineStr">
+        <is>
+          <t>Non-IDP</t>
+        </is>
+      </c>
+      <c r="E110" t="inlineStr">
+        <is>
+          <t>non_idp_NG034002_supp5</t>
+        </is>
+      </c>
+      <c r="F110" t="inlineStr"/>
+      <c r="G110" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="H110" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" t="inlineStr">
+        <is>
+          <t>Sokoto</t>
+        </is>
+      </c>
+      <c r="B111" t="inlineStr">
+        <is>
+          <t>Tambuwal</t>
+        </is>
+      </c>
+      <c r="C111" t="inlineStr">
+        <is>
+          <t>Barkeji-Nabaguda</t>
+        </is>
+      </c>
+      <c r="D111" t="inlineStr">
+        <is>
+          <t>Non-IDP</t>
+        </is>
+      </c>
+      <c r="E111" t="inlineStr">
+        <is>
+          <t>non_idp_NG034018_supp1</t>
+        </is>
+      </c>
+      <c r="F111" t="inlineStr"/>
+      <c r="G111" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="H111" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" t="inlineStr">
+        <is>
+          <t>Sokoto</t>
+        </is>
+      </c>
+      <c r="B112" t="inlineStr">
+        <is>
+          <t>Tambuwal</t>
+        </is>
+      </c>
+      <c r="C112" t="inlineStr">
+        <is>
+          <t>Bagida</t>
+        </is>
+      </c>
+      <c r="D112" t="inlineStr">
+        <is>
+          <t>Non-IDP</t>
+        </is>
+      </c>
+      <c r="E112" t="inlineStr">
+        <is>
+          <t>non_idp_NG034018_supp3</t>
+        </is>
+      </c>
+      <c r="F112" t="inlineStr"/>
+      <c r="G112" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="H112" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" t="inlineStr">
+        <is>
+          <t>Sokoto</t>
+        </is>
+      </c>
+      <c r="B113" t="inlineStr">
+        <is>
+          <t>Gwadabawa</t>
+        </is>
+      </c>
+      <c r="C113" t="inlineStr">
+        <is>
+          <t>Chimola</t>
+        </is>
+      </c>
+      <c r="D113" t="inlineStr">
+        <is>
+          <t>Non-IDP</t>
+        </is>
+      </c>
+      <c r="E113" t="inlineStr">
+        <is>
+          <t>non_idp_NG034005_supp1</t>
+        </is>
+      </c>
+      <c r="F113" t="inlineStr"/>
+      <c r="G113" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="H113" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" t="inlineStr">
+        <is>
+          <t>Sokoto</t>
+        </is>
+      </c>
+      <c r="B114" t="inlineStr">
+        <is>
+          <t>Gwadabawa</t>
+        </is>
+      </c>
+      <c r="C114" t="inlineStr">
+        <is>
+          <t>Darna Tsolawo</t>
+        </is>
+      </c>
+      <c r="D114" t="inlineStr">
+        <is>
+          <t>Non-IDP</t>
+        </is>
+      </c>
+      <c r="E114" t="inlineStr">
+        <is>
+          <t>non_idp_NG034005_supp11</t>
+        </is>
+      </c>
+      <c r="F114" t="inlineStr"/>
+      <c r="G114" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="H114" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" t="inlineStr">
+        <is>
+          <t>Sokoto</t>
+        </is>
+      </c>
+      <c r="B115" t="inlineStr">
+        <is>
+          <t>Gwadabawa</t>
+        </is>
+      </c>
+      <c r="C115" t="inlineStr">
+        <is>
+          <t>Gidan Kaya</t>
+        </is>
+      </c>
+      <c r="D115" t="inlineStr">
+        <is>
+          <t>Non-IDP</t>
+        </is>
+      </c>
+      <c r="E115" t="inlineStr">
+        <is>
+          <t>non_idp_NG034005_supp2</t>
+        </is>
+      </c>
+      <c r="F115" t="inlineStr"/>
+      <c r="G115" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="H115" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" t="inlineStr">
+        <is>
+          <t>Sokoto</t>
+        </is>
+      </c>
+      <c r="B116" t="inlineStr">
+        <is>
+          <t>Gwadabawa</t>
+        </is>
+      </c>
+      <c r="C116" t="inlineStr">
+        <is>
+          <t>Asara</t>
+        </is>
+      </c>
+      <c r="D116" t="inlineStr">
+        <is>
+          <t>Non-IDP</t>
+        </is>
+      </c>
+      <c r="E116" t="inlineStr">
+        <is>
+          <t>non_idp_NG034005_supp3</t>
+        </is>
+      </c>
+      <c r="F116" t="inlineStr"/>
+      <c r="G116" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="H116" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" t="inlineStr">
+        <is>
+          <t>Sokoto</t>
+        </is>
+      </c>
+      <c r="B117" t="inlineStr">
+        <is>
+          <t>Gwadabawa</t>
+        </is>
+      </c>
+      <c r="C117" t="inlineStr">
+        <is>
+          <t>Gwadabawa</t>
+        </is>
+      </c>
+      <c r="D117" t="inlineStr">
+        <is>
+          <t>Non-IDP</t>
+        </is>
+      </c>
+      <c r="E117" t="inlineStr">
+        <is>
+          <t>non_idp_NG034005_supp4</t>
+        </is>
+      </c>
+      <c r="F117" t="inlineStr"/>
+      <c r="G117" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="H117" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" t="inlineStr">
+        <is>
+          <t>Sokoto</t>
+        </is>
+      </c>
+      <c r="B118" t="inlineStr">
+        <is>
+          <t>Gwadabawa</t>
+        </is>
+      </c>
+      <c r="C118" t="inlineStr">
+        <is>
+          <t>Gidan Kaya</t>
+        </is>
+      </c>
+      <c r="D118" t="inlineStr">
+        <is>
+          <t>Non-IDP</t>
+        </is>
+      </c>
+      <c r="E118" t="inlineStr">
+        <is>
+          <t>non_idp_NG034005_supp6</t>
+        </is>
+      </c>
+      <c r="F118" t="inlineStr"/>
+      <c r="G118" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="H118" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" t="inlineStr">
+        <is>
+          <t>Sokoto</t>
+        </is>
+      </c>
+      <c r="B119" t="inlineStr">
+        <is>
+          <t>Gwadabawa</t>
+        </is>
+      </c>
+      <c r="C119" t="inlineStr">
+        <is>
+          <t>Asara</t>
+        </is>
+      </c>
+      <c r="D119" t="inlineStr">
+        <is>
+          <t>Non-IDP</t>
+        </is>
+      </c>
+      <c r="E119" t="inlineStr">
+        <is>
+          <t>non_idp_NG034005_supp9</t>
+        </is>
+      </c>
+      <c r="F119" t="inlineStr"/>
+      <c r="G119" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="H119" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" t="inlineStr">
+        <is>
+          <t>Sokoto</t>
+        </is>
+      </c>
+      <c r="B120" t="inlineStr">
+        <is>
+          <t>Bodinga</t>
+        </is>
+      </c>
+      <c r="C120" t="inlineStr">
+        <is>
+          <t>Darhela Badau</t>
+        </is>
+      </c>
+      <c r="D120" t="inlineStr">
+        <is>
+          <t>Non-IDP</t>
+        </is>
+      </c>
+      <c r="E120" t="inlineStr">
+        <is>
+          <t>non_idp_NG034002_supp8</t>
+        </is>
+      </c>
+      <c r="F120" t="inlineStr"/>
+      <c r="G120" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="H120" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" t="inlineStr">
+        <is>
+          <t>Sokoto</t>
+        </is>
+      </c>
+      <c r="B121" t="inlineStr">
+        <is>
+          <t>Bodinga</t>
+        </is>
+      </c>
+      <c r="C121" t="inlineStr">
+        <is>
+          <t>Sifawa Lukuyawa</t>
+        </is>
+      </c>
+      <c r="D121" t="inlineStr">
+        <is>
+          <t>Non-IDP</t>
+        </is>
+      </c>
+      <c r="E121" t="inlineStr">
+        <is>
+          <t>non_idp_NG034002_supp9</t>
+        </is>
+      </c>
+      <c r="F121" t="inlineStr"/>
+      <c r="G121" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="H121" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" t="inlineStr">
+        <is>
+          <t>Sokoto</t>
+        </is>
+      </c>
+      <c r="B122" t="inlineStr">
+        <is>
+          <t>Bodinga</t>
+        </is>
+      </c>
+      <c r="C122" t="inlineStr">
+        <is>
+          <t>Kaura Miyo</t>
+        </is>
+      </c>
+      <c r="D122" t="inlineStr">
+        <is>
+          <t>Non-IDP</t>
+        </is>
+      </c>
+      <c r="E122" t="inlineStr">
+        <is>
+          <t>non_idp_NG034002_supp10</t>
+        </is>
+      </c>
+      <c r="F122" t="inlineStr"/>
+      <c r="G122" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="H122" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" t="inlineStr">
+        <is>
+          <t>Sokoto</t>
+        </is>
+      </c>
+      <c r="B123" t="inlineStr">
+        <is>
+          <t>Gwadabawa</t>
+        </is>
+      </c>
+      <c r="C123" t="inlineStr">
+        <is>
+          <t>Gidan Kaya</t>
+        </is>
+      </c>
+      <c r="D123" t="inlineStr">
+        <is>
+          <t>Non-IDP</t>
+        </is>
+      </c>
+      <c r="E123" t="inlineStr">
+        <is>
+          <t>non_idp_NG034005_supp12</t>
+        </is>
+      </c>
+      <c r="F123" t="inlineStr"/>
+      <c r="G123" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="H123" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" t="inlineStr">
+        <is>
+          <t>Sokoto</t>
+        </is>
+      </c>
+      <c r="B124" t="inlineStr">
+        <is>
+          <t>Gwadabawa</t>
+        </is>
+      </c>
+      <c r="C124" t="inlineStr">
+        <is>
+          <t>Asara</t>
+        </is>
+      </c>
+      <c r="D124" t="inlineStr">
+        <is>
+          <t>Non-IDP</t>
+        </is>
+      </c>
+      <c r="E124" t="inlineStr">
+        <is>
+          <t>non_idp_NG034005_supp13</t>
+        </is>
+      </c>
+      <c r="F124" t="inlineStr"/>
+      <c r="G124" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="H124" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" t="inlineStr">
+        <is>
+          <t>Sokoto</t>
+        </is>
+      </c>
+      <c r="B125" t="inlineStr">
+        <is>
+          <t>Gwadabawa</t>
+        </is>
+      </c>
+      <c r="C125" t="inlineStr">
+        <is>
+          <t>Gidan Kaya</t>
+        </is>
+      </c>
+      <c r="D125" t="inlineStr">
+        <is>
+          <t>Non-IDP</t>
+        </is>
+      </c>
+      <c r="E125" t="inlineStr">
+        <is>
+          <t>non_idp_NG034005_supp14</t>
+        </is>
+      </c>
+      <c r="F125" t="inlineStr"/>
+      <c r="G125" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="H125" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" t="inlineStr">
+        <is>
+          <t>Sokoto</t>
+        </is>
+      </c>
+      <c r="B126" t="inlineStr">
+        <is>
+          <t>Gwadabawa</t>
+        </is>
+      </c>
+      <c r="C126" t="inlineStr">
+        <is>
+          <t>Gidan Kaya</t>
+        </is>
+      </c>
+      <c r="D126" t="inlineStr">
+        <is>
+          <t>Non-IDP</t>
+        </is>
+      </c>
+      <c r="E126" t="inlineStr">
+        <is>
+          <t>non_idp_NG034005_supp15</t>
+        </is>
+      </c>
+      <c r="F126" t="inlineStr"/>
+      <c r="G126" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="H126" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" t="inlineStr">
+        <is>
+          <t>Sokoto</t>
+        </is>
+      </c>
+      <c r="B127" t="inlineStr">
+        <is>
+          <t>Rabah</t>
+        </is>
+      </c>
+      <c r="C127" t="inlineStr">
+        <is>
+          <t>Rarah</t>
+        </is>
+      </c>
+      <c r="D127" t="inlineStr">
+        <is>
+          <t>Non-IDP</t>
+        </is>
+      </c>
+      <c r="E127" t="inlineStr">
+        <is>
+          <t>non_idp_NG034012_supp1</t>
+        </is>
+      </c>
+      <c r="F127" t="inlineStr"/>
+      <c r="G127" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="H127" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" t="inlineStr">
+        <is>
+          <t>Sokoto</t>
+        </is>
+      </c>
+      <c r="B128" t="inlineStr">
+        <is>
+          <t>Rabah</t>
+        </is>
+      </c>
+      <c r="C128" t="inlineStr">
+        <is>
+          <t>Tsamiya</t>
+        </is>
+      </c>
+      <c r="D128" t="inlineStr">
+        <is>
+          <t>Non-IDP</t>
+        </is>
+      </c>
+      <c r="E128" t="inlineStr">
+        <is>
+          <t>non_idp_NG034012_supp2</t>
+        </is>
+      </c>
+      <c r="F128" t="inlineStr"/>
+      <c r="G128" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="H128" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" t="inlineStr">
+        <is>
+          <t>Sokoto</t>
+        </is>
+      </c>
+      <c r="B129" t="inlineStr">
+        <is>
+          <t>Tambuwal</t>
+        </is>
+      </c>
+      <c r="C129" t="inlineStr">
+        <is>
+          <t>Barkeji-Nabaguda</t>
+        </is>
+      </c>
+      <c r="D129" t="inlineStr">
+        <is>
+          <t>Non-IDP</t>
+        </is>
+      </c>
+      <c r="E129" t="inlineStr">
+        <is>
+          <t>non_idp_NG034018_supp4</t>
+        </is>
+      </c>
+      <c r="F129" t="inlineStr"/>
+      <c r="G129" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="H129" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" t="inlineStr">
+        <is>
+          <t>Sokoto</t>
+        </is>
+      </c>
+      <c r="B130" t="inlineStr">
+        <is>
+          <t>Tambuwal</t>
+        </is>
+      </c>
+      <c r="C130" t="inlineStr">
+        <is>
+          <t>Barkeji-Nabaguda</t>
+        </is>
+      </c>
+      <c r="D130" t="inlineStr">
+        <is>
+          <t>Non-IDP</t>
+        </is>
+      </c>
+      <c r="E130" t="inlineStr">
+        <is>
+          <t>non_idp_NG034018_supp5</t>
+        </is>
+      </c>
+      <c r="F130" t="inlineStr"/>
+      <c r="G130" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="H130" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" t="inlineStr">
+        <is>
+          <t>Sokoto</t>
+        </is>
+      </c>
+      <c r="B131" t="inlineStr">
+        <is>
+          <t>Gwadabawa</t>
+        </is>
+      </c>
+      <c r="C131" t="inlineStr">
+        <is>
+          <t>Gwadabawa</t>
+        </is>
+      </c>
+      <c r="D131" t="inlineStr">
+        <is>
+          <t>IDP</t>
+        </is>
+      </c>
+      <c r="E131" t="inlineStr">
+        <is>
+          <t>idp_NG034005_supp1</t>
+        </is>
+      </c>
+      <c r="F131" t="inlineStr">
+        <is>
+          <t>In-host</t>
+        </is>
+      </c>
+      <c r="G131" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="H131" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+    </row>
+    <row r="132">
+      <c r="A132" t="inlineStr">
+        <is>
+          <t>Sokoto</t>
+        </is>
+      </c>
+      <c r="B132" t="inlineStr">
+        <is>
+          <t>Goronyo</t>
+        </is>
+      </c>
+      <c r="C132" t="inlineStr">
+        <is>
+          <t>Goronyo</t>
+        </is>
+      </c>
+      <c r="D132" t="inlineStr">
+        <is>
+          <t>IDP</t>
+        </is>
+      </c>
+      <c r="E132" t="inlineStr">
+        <is>
+          <t>idp_NG034006_supp1</t>
+        </is>
+      </c>
+      <c r="F132" t="inlineStr">
+        <is>
+          <t>In-host</t>
+        </is>
+      </c>
+      <c r="G132" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="H132" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133" t="inlineStr">
+        <is>
+          <t>Sokoto</t>
+        </is>
+      </c>
+      <c r="B133" t="inlineStr">
+        <is>
+          <t>Goronyo</t>
+        </is>
+      </c>
+      <c r="C133" t="inlineStr">
+        <is>
+          <t>Shinaka</t>
+        </is>
+      </c>
+      <c r="D133" t="inlineStr">
+        <is>
+          <t>IDP</t>
+        </is>
+      </c>
+      <c r="E133" t="inlineStr">
+        <is>
+          <t>idp_NG034006_supp2</t>
+        </is>
+      </c>
+      <c r="F133" t="inlineStr">
+        <is>
+          <t>In-host</t>
+        </is>
+      </c>
+      <c r="G133" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="H133" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+    </row>
+    <row r="134">
+      <c r="A134" t="inlineStr">
+        <is>
+          <t>Sokoto</t>
+        </is>
+      </c>
+      <c r="B134" t="inlineStr">
+        <is>
+          <t>Rabah</t>
+        </is>
+      </c>
+      <c r="C134" t="inlineStr">
+        <is>
+          <t>Rabah</t>
+        </is>
+      </c>
+      <c r="D134" t="inlineStr">
+        <is>
+          <t>IDP</t>
+        </is>
+      </c>
+      <c r="E134" t="inlineStr">
+        <is>
+          <t>idp_NG034012_supp1</t>
+        </is>
+      </c>
+      <c r="F134" t="inlineStr">
+        <is>
+          <t>In-host</t>
+        </is>
+      </c>
+      <c r="G134" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="H134" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+    </row>
+    <row r="135">
+      <c r="A135" t="inlineStr">
+        <is>
+          <t>Sokoto</t>
+        </is>
+      </c>
+      <c r="B135" t="inlineStr">
+        <is>
+          <t>Rabah</t>
+        </is>
+      </c>
+      <c r="C135" t="inlineStr">
+        <is>
+          <t>Rabah</t>
+        </is>
+      </c>
+      <c r="D135" t="inlineStr">
+        <is>
+          <t>IDP</t>
+        </is>
+      </c>
+      <c r="E135" t="inlineStr">
+        <is>
+          <t>idp_NG034012_supp2</t>
+        </is>
+      </c>
+      <c r="F135" t="inlineStr">
+        <is>
+          <t>In-camp</t>
+        </is>
+      </c>
+      <c r="G135" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="H135" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+    </row>
+    <row r="136">
+      <c r="A136" t="inlineStr">
+        <is>
+          <t>Sokoto</t>
+        </is>
+      </c>
+      <c r="B136" t="inlineStr">
+        <is>
+          <t>Rabah</t>
+        </is>
+      </c>
+      <c r="C136" t="inlineStr">
+        <is>
+          <t>Rabah</t>
+        </is>
+      </c>
+      <c r="D136" t="inlineStr">
+        <is>
+          <t>IDP</t>
+        </is>
+      </c>
+      <c r="E136" t="inlineStr">
+        <is>
+          <t>idp_NG034012_supp3</t>
+        </is>
+      </c>
+      <c r="F136" t="inlineStr">
+        <is>
+          <t>In-host</t>
+        </is>
+      </c>
+      <c r="G136" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="H136" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+    </row>
+    <row r="137">
+      <c r="A137" t="inlineStr">
+        <is>
+          <t>Sokoto</t>
+        </is>
+      </c>
+      <c r="B137" t="inlineStr">
+        <is>
+          <t>Rabah</t>
+        </is>
+      </c>
+      <c r="C137" t="inlineStr">
+        <is>
+          <t>Gandi 1</t>
+        </is>
+      </c>
+      <c r="D137" t="inlineStr">
+        <is>
+          <t>IDP</t>
+        </is>
+      </c>
+      <c r="E137" t="inlineStr">
+        <is>
+          <t>idp_NG034012_supp4</t>
+        </is>
+      </c>
+      <c r="F137" t="inlineStr">
+        <is>
+          <t>In-camp</t>
+        </is>
+      </c>
+      <c r="G137" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="H137" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+    </row>
+    <row r="138">
+      <c r="A138" t="inlineStr">
+        <is>
+          <t>Sokoto</t>
+        </is>
+      </c>
+      <c r="B138" t="inlineStr">
+        <is>
+          <t>Rabah</t>
+        </is>
+      </c>
+      <c r="C138" t="inlineStr">
+        <is>
+          <t>Gandi 1</t>
+        </is>
+      </c>
+      <c r="D138" t="inlineStr">
+        <is>
+          <t>IDP</t>
+        </is>
+      </c>
+      <c r="E138" t="inlineStr">
+        <is>
+          <t>idp_NG034012_supp5</t>
+        </is>
+      </c>
+      <c r="F138" t="inlineStr">
+        <is>
+          <t>In-camp</t>
+        </is>
+      </c>
+      <c r="G138" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="H138" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+    </row>
+    <row r="139">
+      <c r="A139" t="inlineStr">
+        <is>
+          <t>Sokoto</t>
+        </is>
+      </c>
+      <c r="B139" t="inlineStr">
+        <is>
+          <t>Rabah</t>
+        </is>
+      </c>
+      <c r="C139" t="inlineStr">
+        <is>
+          <t>Gandi 1</t>
+        </is>
+      </c>
+      <c r="D139" t="inlineStr">
+        <is>
+          <t>IDP</t>
+        </is>
+      </c>
+      <c r="E139" t="inlineStr">
+        <is>
+          <t>idp_NG034012_supp6</t>
+        </is>
+      </c>
+      <c r="F139" t="inlineStr">
+        <is>
+          <t>In-host</t>
+        </is>
+      </c>
+      <c r="G139" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="H139" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+    </row>
+    <row r="140">
+      <c r="A140" t="inlineStr">
+        <is>
+          <t>Sokoto</t>
+        </is>
+      </c>
+      <c r="B140" t="inlineStr">
+        <is>
+          <t>Rabah</t>
+        </is>
+      </c>
+      <c r="C140" t="inlineStr">
+        <is>
+          <t>Gandi 1</t>
+        </is>
+      </c>
+      <c r="D140" t="inlineStr">
+        <is>
+          <t>IDP</t>
+        </is>
+      </c>
+      <c r="E140" t="inlineStr">
+        <is>
+          <t>idp_NG034012_supp7</t>
+        </is>
+      </c>
+      <c r="F140" t="inlineStr">
+        <is>
+          <t>In-camp</t>
+        </is>
+      </c>
+      <c r="G140" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="H140" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+    </row>
+    <row r="141">
+      <c r="A141" t="inlineStr">
+        <is>
+          <t>Sokoto</t>
+        </is>
+      </c>
+      <c r="B141" t="inlineStr">
+        <is>
+          <t>Tambuwal</t>
+        </is>
+      </c>
+      <c r="C141" t="inlineStr">
+        <is>
+          <t>Sabon Birni</t>
+        </is>
+      </c>
+      <c r="D141" t="inlineStr">
+        <is>
+          <t>IDP</t>
+        </is>
+      </c>
+      <c r="E141" t="inlineStr">
+        <is>
+          <t>idp_NG034018_supp1</t>
+        </is>
+      </c>
+      <c r="F141" t="inlineStr">
+        <is>
+          <t>In-host</t>
+        </is>
+      </c>
+      <c r="G141" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="H141" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+    </row>
+    <row r="142">
+      <c r="A142" t="inlineStr">
+        <is>
+          <t>Sokoto</t>
+        </is>
+      </c>
+      <c r="B142" t="inlineStr">
+        <is>
+          <t>Tambuwal</t>
+        </is>
+      </c>
+      <c r="C142" t="inlineStr">
+        <is>
+          <t>Sabon Birni</t>
+        </is>
+      </c>
+      <c r="D142" t="inlineStr">
+        <is>
+          <t>IDP</t>
+        </is>
+      </c>
+      <c r="E142" t="inlineStr">
+        <is>
+          <t>idp_NG034018_supp2</t>
+        </is>
+      </c>
+      <c r="F142" t="inlineStr">
+        <is>
+          <t>In-host</t>
+        </is>
+      </c>
+      <c r="G142" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="H142" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+    </row>
+    <row r="143">
+      <c r="A143" t="inlineStr">
+        <is>
+          <t>Sokoto</t>
+        </is>
+      </c>
+      <c r="B143" t="inlineStr">
+        <is>
+          <t>Tambuwal</t>
+        </is>
+      </c>
+      <c r="C143" t="inlineStr">
+        <is>
+          <t>Sabon Birni</t>
+        </is>
+      </c>
+      <c r="D143" t="inlineStr">
+        <is>
+          <t>IDP</t>
+        </is>
+      </c>
+      <c r="E143" t="inlineStr">
+        <is>
+          <t>idp_NG034018_supp4</t>
+        </is>
+      </c>
+      <c r="F143" t="inlineStr">
+        <is>
+          <t>In-camp</t>
+        </is>
+      </c>
+      <c r="G143" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="H143" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+    </row>
+    <row r="144">
+      <c r="A144" t="inlineStr">
+        <is>
+          <t>Sokoto</t>
+        </is>
+      </c>
+      <c r="B144" t="inlineStr">
+        <is>
+          <t>Gwadabawa</t>
+        </is>
+      </c>
+      <c r="C144" t="inlineStr">
+        <is>
+          <t>Gwadabawa</t>
+        </is>
+      </c>
+      <c r="D144" t="inlineStr">
+        <is>
+          <t>IDP</t>
+        </is>
+      </c>
+      <c r="E144" t="inlineStr">
+        <is>
+          <t>idp_NG034005_supp2</t>
+        </is>
+      </c>
+      <c r="F144" t="inlineStr">
+        <is>
+          <t>In-host</t>
+        </is>
+      </c>
+      <c r="G144" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="H144" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <dataValidations count="2">
-    <dataValidation sqref="I2:I108" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="I2:I144" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"Yes,No"</formula1>
     </dataValidation>
-    <dataValidation sqref="J2:J108" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="J2:J144" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"N/A - fully accessible,Insecurity / conflict,Physical access (terrain, flooding, roads),Population absent / relocated,Building-footprint issue (no eligible structures),Access denied by authorities / community,Other"</formula1>
     </dataValidation>
   </dataValidations>
@@ -11348,13 +12762,13 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{081A60EB-E903-4C1B-9E47-2759C8E4A581}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{9EF43982-CEA3-4841-920A-2DC16DE69466}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{2471CA07-69A1-4204-93DB-0B74ADA107E6}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{051762B2-E3B1-4F83-B3D9-2AAA9F171B4E}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{17EDB3AA-518C-41FA-BE13-1298B3B58AAD}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{CEFE826F-FAEB-48E2-AF9F-7B36B5819B6A}"/>
 </file>
--- a/resampling/input/accessibility_reports_returned/ACF_accessibility_report.xlsx
+++ b/resampling/input/accessibility_reports_returned/ACF_accessibility_report.xlsx
@@ -12504,271 +12504,4 @@
     <tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
   </tableParts>
 </worksheet>
-</file>
-
-<file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x01010064B5BF8B0F90A143B1A4ACAD04008153" ma:contentTypeVersion="15" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="ada0274d0d067bbbdece3301958c05ce">
-  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="30973102-2308-455b-8e1f-b6a90edc3b23" xmlns:ns3="947c1918-d5ab-48a1-8b61-0d52f2f99fd1" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="1f05eaaac1f596f0cf4554f8e9f637ce" ns2:_="" ns3:_="">
-    <xsd:import namespace="30973102-2308-455b-8e1f-b6a90edc3b23"/>
-    <xsd:import namespace="947c1918-d5ab-48a1-8b61-0d52f2f99fd1"/>
-    <xsd:element name="properties">
-      <xsd:complexType>
-        <xsd:sequence>
-          <xsd:element name="documentManagement">
-            <xsd:complexType>
-              <xsd:all>
-                <xsd:element ref="ns2:MediaServiceMetadata" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceFastMetadata" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceObjectDetectorVersions" minOccurs="0"/>
-                <xsd:element ref="ns2:lcf76f155ced4ddcb4097134ff3c332f" minOccurs="0"/>
-                <xsd:element ref="ns3:TaxCatchAll" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceOCR" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceGenerationTime" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceEventHashCode" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceDateTaken" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaLengthInSeconds" minOccurs="0"/>
-                <xsd:element ref="ns3:SharedWithUsers" minOccurs="0"/>
-                <xsd:element ref="ns3:SharedWithDetails" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceLocation" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceSearchProperties" minOccurs="0"/>
-              </xsd:all>
-            </xsd:complexType>
-          </xsd:element>
-        </xsd:sequence>
-      </xsd:complexType>
-    </xsd:element>
-  </xsd:schema>
-  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:dms="http://schemas.microsoft.com/office/2006/documentManagement/types" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" targetNamespace="30973102-2308-455b-8e1f-b6a90edc3b23" elementFormDefault="qualified">
-    <xsd:import namespace="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
-    <xsd:import namespace="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <xsd:element name="MediaServiceMetadata" ma:index="8" nillable="true" ma:displayName="MediaServiceMetadata" ma:hidden="true" ma:internalName="MediaServiceMetadata" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Note"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceFastMetadata" ma:index="9" nillable="true" ma:displayName="MediaServiceFastMetadata" ma:hidden="true" ma:internalName="MediaServiceFastMetadata" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Note"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceObjectDetectorVersions" ma:index="10" nillable="true" ma:displayName="MediaServiceObjectDetectorVersions" ma:hidden="true" ma:indexed="true" ma:internalName="MediaServiceObjectDetectorVersions" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Text"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="lcf76f155ced4ddcb4097134ff3c332f" ma:index="12" nillable="true" ma:taxonomy="true" ma:internalName="lcf76f155ced4ddcb4097134ff3c332f" ma:taxonomyFieldName="MediaServiceImageTags" ma:displayName="Image Tags" ma:readOnly="false" ma:fieldId="{5cf76f15-5ced-4ddc-b409-7134ff3c332f}" ma:taxonomyMulti="true" ma:sspId="4d06f0b5-5743-41f2-90d3-b12c8ffc7f36" ma:termSetId="09814cd3-568e-fe90-9814-8d621ff8fb84" ma:anchorId="fba54fb3-c3e1-fe81-a776-ca4b69148c4d" ma:open="true" ma:isKeyword="false">
-      <xsd:complexType>
-        <xsd:sequence>
-          <xsd:element ref="pc:Terms" minOccurs="0" maxOccurs="1"/>
-        </xsd:sequence>
-      </xsd:complexType>
-    </xsd:element>
-    <xsd:element name="MediaServiceOCR" ma:index="14" nillable="true" ma:displayName="Extracted Text" ma:internalName="MediaServiceOCR" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Note">
-          <xsd:maxLength value="255"/>
-        </xsd:restriction>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceGenerationTime" ma:index="15" nillable="true" ma:displayName="MediaServiceGenerationTime" ma:hidden="true" ma:internalName="MediaServiceGenerationTime" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Text"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceEventHashCode" ma:index="16" nillable="true" ma:displayName="MediaServiceEventHashCode" ma:hidden="true" ma:internalName="MediaServiceEventHashCode" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Text"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceDateTaken" ma:index="17" nillable="true" ma:displayName="MediaServiceDateTaken" ma:hidden="true" ma:indexed="true" ma:internalName="MediaServiceDateTaken" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Text"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaLengthInSeconds" ma:index="18" nillable="true" ma:displayName="MediaLengthInSeconds" ma:hidden="true" ma:internalName="MediaLengthInSeconds" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Unknown"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceLocation" ma:index="21" nillable="true" ma:displayName="Location" ma:description="" ma:indexed="true" ma:internalName="MediaServiceLocation" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Text"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceSearchProperties" ma:index="22" nillable="true" ma:displayName="MediaServiceSearchProperties" ma:hidden="true" ma:internalName="MediaServiceSearchProperties" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Note"/>
-      </xsd:simpleType>
-    </xsd:element>
-  </xsd:schema>
-  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:dms="http://schemas.microsoft.com/office/2006/documentManagement/types" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" targetNamespace="947c1918-d5ab-48a1-8b61-0d52f2f99fd1" elementFormDefault="qualified">
-    <xsd:import namespace="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
-    <xsd:import namespace="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <xsd:element name="TaxCatchAll" ma:index="13" nillable="true" ma:displayName="Taxonomy Catch All Column" ma:hidden="true" ma:list="{daf5bdda-bc47-491d-9935-b3e42d5c0ae4}" ma:internalName="TaxCatchAll" ma:showField="CatchAllData" ma:web="947c1918-d5ab-48a1-8b61-0d52f2f99fd1">
-      <xsd:complexType>
-        <xsd:complexContent>
-          <xsd:extension base="dms:MultiChoiceLookup">
-            <xsd:sequence>
-              <xsd:element name="Value" type="dms:Lookup" maxOccurs="unbounded" minOccurs="0" nillable="true"/>
-            </xsd:sequence>
-          </xsd:extension>
-        </xsd:complexContent>
-      </xsd:complexType>
-    </xsd:element>
-    <xsd:element name="SharedWithUsers" ma:index="19" nillable="true" ma:displayName="Shared With" ma:internalName="SharedWithUsers" ma:readOnly="true">
-      <xsd:complexType>
-        <xsd:complexContent>
-          <xsd:extension base="dms:UserMulti">
-            <xsd:sequence>
-              <xsd:element name="UserInfo" minOccurs="0" maxOccurs="unbounded">
-                <xsd:complexType>
-                  <xsd:sequence>
-                    <xsd:element name="DisplayName" type="xsd:string" minOccurs="0"/>
-                    <xsd:element name="AccountId" type="dms:UserId" minOccurs="0" nillable="true"/>
-                    <xsd:element name="AccountType" type="xsd:string" minOccurs="0"/>
-                  </xsd:sequence>
-                </xsd:complexType>
-              </xsd:element>
-            </xsd:sequence>
-          </xsd:extension>
-        </xsd:complexContent>
-      </xsd:complexType>
-    </xsd:element>
-    <xsd:element name="SharedWithDetails" ma:index="20" nillable="true" ma:displayName="Shared With Details" ma:internalName="SharedWithDetails" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Note">
-          <xsd:maxLength value="255"/>
-        </xsd:restriction>
-      </xsd:simpleType>
-    </xsd:element>
-  </xsd:schema>
-  <xsd:schema xmlns="http://schemas.openxmlformats.org/package/2006/metadata/core-properties" xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:dc="http://purl.org/dc/elements/1.1/" xmlns:dcterms="http://purl.org/dc/terms/" xmlns:odoc="http://schemas.microsoft.com/internal/obd" targetNamespace="http://schemas.openxmlformats.org/package/2006/metadata/core-properties" elementFormDefault="qualified" attributeFormDefault="unqualified" blockDefault="#all">
-    <xsd:import namespace="http://purl.org/dc/elements/1.1/" schemaLocation="http://dublincore.org/schemas/xmls/qdc/2003/04/02/dc.xsd"/>
-    <xsd:import namespace="http://purl.org/dc/terms/" schemaLocation="http://dublincore.org/schemas/xmls/qdc/2003/04/02/dcterms.xsd"/>
-    <xsd:element name="coreProperties" type="CT_coreProperties"/>
-    <xsd:complexType name="CT_coreProperties">
-      <xsd:all>
-        <xsd:element ref="dc:creator" minOccurs="0" maxOccurs="1"/>
-        <xsd:element ref="dcterms:created" minOccurs="0" maxOccurs="1"/>
-        <xsd:element ref="dc:identifier" minOccurs="0" maxOccurs="1"/>
-        <xsd:element name="contentType" minOccurs="0" maxOccurs="1" type="xsd:string" ma:index="0" ma:displayName="Content Type"/>
-        <xsd:element ref="dc:title" minOccurs="0" maxOccurs="1" ma:index="4" ma:displayName="Title"/>
-        <xsd:element ref="dc:subject" minOccurs="0" maxOccurs="1"/>
-        <xsd:element ref="dc:description" minOccurs="0" maxOccurs="1"/>
-        <xsd:element name="keywords" minOccurs="0" maxOccurs="1" type="xsd:string"/>
-        <xsd:element ref="dc:language" minOccurs="0" maxOccurs="1"/>
-        <xsd:element name="category" minOccurs="0" maxOccurs="1" type="xsd:string"/>
-        <xsd:element name="version" minOccurs="0" maxOccurs="1" type="xsd:string"/>
-        <xsd:element name="revision" minOccurs="0" maxOccurs="1" type="xsd:string">
-          <xsd:annotation>
-            <xsd:documentation>
-                        This value indicates the number of saves or revisions. The application is responsible for updating this value after each revision.
-                    </xsd:documentation>
-          </xsd:annotation>
-        </xsd:element>
-        <xsd:element name="lastModifiedBy" minOccurs="0" maxOccurs="1" type="xsd:string"/>
-        <xsd:element ref="dcterms:modified" minOccurs="0" maxOccurs="1"/>
-        <xsd:element name="contentStatus" minOccurs="0" maxOccurs="1" type="xsd:string"/>
-      </xsd:all>
-    </xsd:complexType>
-  </xsd:schema>
-  <xs:schema xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" xmlns:xs="http://www.w3.org/2001/XMLSchema" targetNamespace="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" elementFormDefault="qualified" attributeFormDefault="unqualified">
-    <xs:element name="Person">
-      <xs:complexType>
-        <xs:sequence>
-          <xs:element ref="pc:DisplayName" minOccurs="0"/>
-          <xs:element ref="pc:AccountId" minOccurs="0"/>
-          <xs:element ref="pc:AccountType" minOccurs="0"/>
-        </xs:sequence>
-      </xs:complexType>
-    </xs:element>
-    <xs:element name="DisplayName" type="xs:string"/>
-    <xs:element name="AccountId" type="xs:string"/>
-    <xs:element name="AccountType" type="xs:string"/>
-    <xs:element name="BDCAssociatedEntity">
-      <xs:complexType>
-        <xs:sequence>
-          <xs:element ref="pc:BDCEntity" minOccurs="0" maxOccurs="unbounded"/>
-        </xs:sequence>
-        <xs:attribute ref="pc:EntityNamespace"/>
-        <xs:attribute ref="pc:EntityName"/>
-        <xs:attribute ref="pc:SystemInstanceName"/>
-        <xs:attribute ref="pc:AssociationName"/>
-      </xs:complexType>
-    </xs:element>
-    <xs:attribute name="EntityNamespace" type="xs:string"/>
-    <xs:attribute name="EntityName" type="xs:string"/>
-    <xs:attribute name="SystemInstanceName" type="xs:string"/>
-    <xs:attribute name="AssociationName" type="xs:string"/>
-    <xs:element name="BDCEntity">
-      <xs:complexType>
-        <xs:sequence>
-          <xs:element ref="pc:EntityDisplayName" minOccurs="0"/>
-          <xs:element ref="pc:EntityInstanceReference" minOccurs="0"/>
-          <xs:element ref="pc:EntityId1" minOccurs="0"/>
-          <xs:element ref="pc:EntityId2" minOccurs="0"/>
-          <xs:element ref="pc:EntityId3" minOccurs="0"/>
-          <xs:element ref="pc:EntityId4" minOccurs="0"/>
-          <xs:element ref="pc:EntityId5" minOccurs="0"/>
-        </xs:sequence>
-      </xs:complexType>
-    </xs:element>
-    <xs:element name="EntityDisplayName" type="xs:string"/>
-    <xs:element name="EntityInstanceReference" type="xs:string"/>
-    <xs:element name="EntityId1" type="xs:string"/>
-    <xs:element name="EntityId2" type="xs:string"/>
-    <xs:element name="EntityId3" type="xs:string"/>
-    <xs:element name="EntityId4" type="xs:string"/>
-    <xs:element name="EntityId5" type="xs:string"/>
-    <xs:element name="Terms">
-      <xs:complexType>
-        <xs:sequence>
-          <xs:element ref="pc:TermInfo" minOccurs="0" maxOccurs="unbounded"/>
-        </xs:sequence>
-      </xs:complexType>
-    </xs:element>
-    <xs:element name="TermInfo">
-      <xs:complexType>
-        <xs:sequence>
-          <xs:element ref="pc:TermName" minOccurs="0"/>
-          <xs:element ref="pc:TermId" minOccurs="0"/>
-        </xs:sequence>
-      </xs:complexType>
-    </xs:element>
-    <xs:element name="TermName" type="xs:string"/>
-    <xs:element name="TermId" type="xs:string"/>
-  </xs:schema>
-</ct:contentTypeSchema>
-</file>
-
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="30973102-2308-455b-8e1f-b6a90edc3b23">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-    <TaxCatchAll xmlns="947c1918-d5ab-48a1-8b61-0d52f2f99fd1" xsi:nil="true"/>
-  </documentManagement>
-</p:properties>
-</file>
-
-<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{9EF43982-CEA3-4841-920A-2DC16DE69466}"/>
-</file>
-
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{051762B2-E3B1-4F83-B3D9-2AAA9F171B4E}"/>
-</file>
-
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{CEFE826F-FAEB-48E2-AF9F-7B36B5819B6A}"/>
 </file>
--- a/resampling/input/accessibility_reports_returned/ACF_accessibility_report.xlsx
+++ b/resampling/input/accessibility_reports_returned/ACF_accessibility_report.xlsx
@@ -12504,4 +12504,271 @@
     <tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
   </tableParts>
 </worksheet>
+</file>
+
+<file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x01010064B5BF8B0F90A143B1A4ACAD04008153" ma:contentTypeVersion="15" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="ada0274d0d067bbbdece3301958c05ce">
+  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="30973102-2308-455b-8e1f-b6a90edc3b23" xmlns:ns3="947c1918-d5ab-48a1-8b61-0d52f2f99fd1" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="1f05eaaac1f596f0cf4554f8e9f637ce" ns2:_="" ns3:_="">
+    <xsd:import namespace="30973102-2308-455b-8e1f-b6a90edc3b23"/>
+    <xsd:import namespace="947c1918-d5ab-48a1-8b61-0d52f2f99fd1"/>
+    <xsd:element name="properties">
+      <xsd:complexType>
+        <xsd:sequence>
+          <xsd:element name="documentManagement">
+            <xsd:complexType>
+              <xsd:all>
+                <xsd:element ref="ns2:MediaServiceMetadata" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceFastMetadata" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceObjectDetectorVersions" minOccurs="0"/>
+                <xsd:element ref="ns2:lcf76f155ced4ddcb4097134ff3c332f" minOccurs="0"/>
+                <xsd:element ref="ns3:TaxCatchAll" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceOCR" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceGenerationTime" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceEventHashCode" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceDateTaken" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaLengthInSeconds" minOccurs="0"/>
+                <xsd:element ref="ns3:SharedWithUsers" minOccurs="0"/>
+                <xsd:element ref="ns3:SharedWithDetails" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceLocation" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceSearchProperties" minOccurs="0"/>
+              </xsd:all>
+            </xsd:complexType>
+          </xsd:element>
+        </xsd:sequence>
+      </xsd:complexType>
+    </xsd:element>
+  </xsd:schema>
+  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:dms="http://schemas.microsoft.com/office/2006/documentManagement/types" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" targetNamespace="30973102-2308-455b-8e1f-b6a90edc3b23" elementFormDefault="qualified">
+    <xsd:import namespace="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <xsd:import namespace="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <xsd:element name="MediaServiceMetadata" ma:index="8" nillable="true" ma:displayName="MediaServiceMetadata" ma:hidden="true" ma:internalName="MediaServiceMetadata" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceFastMetadata" ma:index="9" nillable="true" ma:displayName="MediaServiceFastMetadata" ma:hidden="true" ma:internalName="MediaServiceFastMetadata" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceObjectDetectorVersions" ma:index="10" nillable="true" ma:displayName="MediaServiceObjectDetectorVersions" ma:hidden="true" ma:indexed="true" ma:internalName="MediaServiceObjectDetectorVersions" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Text"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="lcf76f155ced4ddcb4097134ff3c332f" ma:index="12" nillable="true" ma:taxonomy="true" ma:internalName="lcf76f155ced4ddcb4097134ff3c332f" ma:taxonomyFieldName="MediaServiceImageTags" ma:displayName="Image Tags" ma:readOnly="false" ma:fieldId="{5cf76f15-5ced-4ddc-b409-7134ff3c332f}" ma:taxonomyMulti="true" ma:sspId="4d06f0b5-5743-41f2-90d3-b12c8ffc7f36" ma:termSetId="09814cd3-568e-fe90-9814-8d621ff8fb84" ma:anchorId="fba54fb3-c3e1-fe81-a776-ca4b69148c4d" ma:open="true" ma:isKeyword="false">
+      <xsd:complexType>
+        <xsd:sequence>
+          <xsd:element ref="pc:Terms" minOccurs="0" maxOccurs="1"/>
+        </xsd:sequence>
+      </xsd:complexType>
+    </xsd:element>
+    <xsd:element name="MediaServiceOCR" ma:index="14" nillable="true" ma:displayName="Extracted Text" ma:internalName="MediaServiceOCR" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note">
+          <xsd:maxLength value="255"/>
+        </xsd:restriction>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceGenerationTime" ma:index="15" nillable="true" ma:displayName="MediaServiceGenerationTime" ma:hidden="true" ma:internalName="MediaServiceGenerationTime" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Text"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceEventHashCode" ma:index="16" nillable="true" ma:displayName="MediaServiceEventHashCode" ma:hidden="true" ma:internalName="MediaServiceEventHashCode" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Text"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceDateTaken" ma:index="17" nillable="true" ma:displayName="MediaServiceDateTaken" ma:hidden="true" ma:indexed="true" ma:internalName="MediaServiceDateTaken" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Text"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaLengthInSeconds" ma:index="18" nillable="true" ma:displayName="MediaLengthInSeconds" ma:hidden="true" ma:internalName="MediaLengthInSeconds" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Unknown"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceLocation" ma:index="21" nillable="true" ma:displayName="Location" ma:description="" ma:indexed="true" ma:internalName="MediaServiceLocation" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Text"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceSearchProperties" ma:index="22" nillable="true" ma:displayName="MediaServiceSearchProperties" ma:hidden="true" ma:internalName="MediaServiceSearchProperties" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note"/>
+      </xsd:simpleType>
+    </xsd:element>
+  </xsd:schema>
+  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:dms="http://schemas.microsoft.com/office/2006/documentManagement/types" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" targetNamespace="947c1918-d5ab-48a1-8b61-0d52f2f99fd1" elementFormDefault="qualified">
+    <xsd:import namespace="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <xsd:import namespace="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <xsd:element name="TaxCatchAll" ma:index="13" nillable="true" ma:displayName="Taxonomy Catch All Column" ma:hidden="true" ma:list="{daf5bdda-bc47-491d-9935-b3e42d5c0ae4}" ma:internalName="TaxCatchAll" ma:showField="CatchAllData" ma:web="947c1918-d5ab-48a1-8b61-0d52f2f99fd1">
+      <xsd:complexType>
+        <xsd:complexContent>
+          <xsd:extension base="dms:MultiChoiceLookup">
+            <xsd:sequence>
+              <xsd:element name="Value" type="dms:Lookup" maxOccurs="unbounded" minOccurs="0" nillable="true"/>
+            </xsd:sequence>
+          </xsd:extension>
+        </xsd:complexContent>
+      </xsd:complexType>
+    </xsd:element>
+    <xsd:element name="SharedWithUsers" ma:index="19" nillable="true" ma:displayName="Shared With" ma:internalName="SharedWithUsers" ma:readOnly="true">
+      <xsd:complexType>
+        <xsd:complexContent>
+          <xsd:extension base="dms:UserMulti">
+            <xsd:sequence>
+              <xsd:element name="UserInfo" minOccurs="0" maxOccurs="unbounded">
+                <xsd:complexType>
+                  <xsd:sequence>
+                    <xsd:element name="DisplayName" type="xsd:string" minOccurs="0"/>
+                    <xsd:element name="AccountId" type="dms:UserId" minOccurs="0" nillable="true"/>
+                    <xsd:element name="AccountType" type="xsd:string" minOccurs="0"/>
+                  </xsd:sequence>
+                </xsd:complexType>
+              </xsd:element>
+            </xsd:sequence>
+          </xsd:extension>
+        </xsd:complexContent>
+      </xsd:complexType>
+    </xsd:element>
+    <xsd:element name="SharedWithDetails" ma:index="20" nillable="true" ma:displayName="Shared With Details" ma:internalName="SharedWithDetails" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note">
+          <xsd:maxLength value="255"/>
+        </xsd:restriction>
+      </xsd:simpleType>
+    </xsd:element>
+  </xsd:schema>
+  <xsd:schema xmlns="http://schemas.openxmlformats.org/package/2006/metadata/core-properties" xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:dc="http://purl.org/dc/elements/1.1/" xmlns:dcterms="http://purl.org/dc/terms/" xmlns:odoc="http://schemas.microsoft.com/internal/obd" targetNamespace="http://schemas.openxmlformats.org/package/2006/metadata/core-properties" elementFormDefault="qualified" attributeFormDefault="unqualified" blockDefault="#all">
+    <xsd:import namespace="http://purl.org/dc/elements/1.1/" schemaLocation="http://dublincore.org/schemas/xmls/qdc/2003/04/02/dc.xsd"/>
+    <xsd:import namespace="http://purl.org/dc/terms/" schemaLocation="http://dublincore.org/schemas/xmls/qdc/2003/04/02/dcterms.xsd"/>
+    <xsd:element name="coreProperties" type="CT_coreProperties"/>
+    <xsd:complexType name="CT_coreProperties">
+      <xsd:all>
+        <xsd:element ref="dc:creator" minOccurs="0" maxOccurs="1"/>
+        <xsd:element ref="dcterms:created" minOccurs="0" maxOccurs="1"/>
+        <xsd:element ref="dc:identifier" minOccurs="0" maxOccurs="1"/>
+        <xsd:element name="contentType" minOccurs="0" maxOccurs="1" type="xsd:string" ma:index="0" ma:displayName="Content Type"/>
+        <xsd:element ref="dc:title" minOccurs="0" maxOccurs="1" ma:index="4" ma:displayName="Title"/>
+        <xsd:element ref="dc:subject" minOccurs="0" maxOccurs="1"/>
+        <xsd:element ref="dc:description" minOccurs="0" maxOccurs="1"/>
+        <xsd:element name="keywords" minOccurs="0" maxOccurs="1" type="xsd:string"/>
+        <xsd:element ref="dc:language" minOccurs="0" maxOccurs="1"/>
+        <xsd:element name="category" minOccurs="0" maxOccurs="1" type="xsd:string"/>
+        <xsd:element name="version" minOccurs="0" maxOccurs="1" type="xsd:string"/>
+        <xsd:element name="revision" minOccurs="0" maxOccurs="1" type="xsd:string">
+          <xsd:annotation>
+            <xsd:documentation>
+                        This value indicates the number of saves or revisions. The application is responsible for updating this value after each revision.
+                    </xsd:documentation>
+          </xsd:annotation>
+        </xsd:element>
+        <xsd:element name="lastModifiedBy" minOccurs="0" maxOccurs="1" type="xsd:string"/>
+        <xsd:element ref="dcterms:modified" minOccurs="0" maxOccurs="1"/>
+        <xsd:element name="contentStatus" minOccurs="0" maxOccurs="1" type="xsd:string"/>
+      </xsd:all>
+    </xsd:complexType>
+  </xsd:schema>
+  <xs:schema xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" xmlns:xs="http://www.w3.org/2001/XMLSchema" targetNamespace="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" elementFormDefault="qualified" attributeFormDefault="unqualified">
+    <xs:element name="Person">
+      <xs:complexType>
+        <xs:sequence>
+          <xs:element ref="pc:DisplayName" minOccurs="0"/>
+          <xs:element ref="pc:AccountId" minOccurs="0"/>
+          <xs:element ref="pc:AccountType" minOccurs="0"/>
+        </xs:sequence>
+      </xs:complexType>
+    </xs:element>
+    <xs:element name="DisplayName" type="xs:string"/>
+    <xs:element name="AccountId" type="xs:string"/>
+    <xs:element name="AccountType" type="xs:string"/>
+    <xs:element name="BDCAssociatedEntity">
+      <xs:complexType>
+        <xs:sequence>
+          <xs:element ref="pc:BDCEntity" minOccurs="0" maxOccurs="unbounded"/>
+        </xs:sequence>
+        <xs:attribute ref="pc:EntityNamespace"/>
+        <xs:attribute ref="pc:EntityName"/>
+        <xs:attribute ref="pc:SystemInstanceName"/>
+        <xs:attribute ref="pc:AssociationName"/>
+      </xs:complexType>
+    </xs:element>
+    <xs:attribute name="EntityNamespace" type="xs:string"/>
+    <xs:attribute name="EntityName" type="xs:string"/>
+    <xs:attribute name="SystemInstanceName" type="xs:string"/>
+    <xs:attribute name="AssociationName" type="xs:string"/>
+    <xs:element name="BDCEntity">
+      <xs:complexType>
+        <xs:sequence>
+          <xs:element ref="pc:EntityDisplayName" minOccurs="0"/>
+          <xs:element ref="pc:EntityInstanceReference" minOccurs="0"/>
+          <xs:element ref="pc:EntityId1" minOccurs="0"/>
+          <xs:element ref="pc:EntityId2" minOccurs="0"/>
+          <xs:element ref="pc:EntityId3" minOccurs="0"/>
+          <xs:element ref="pc:EntityId4" minOccurs="0"/>
+          <xs:element ref="pc:EntityId5" minOccurs="0"/>
+        </xs:sequence>
+      </xs:complexType>
+    </xs:element>
+    <xs:element name="EntityDisplayName" type="xs:string"/>
+    <xs:element name="EntityInstanceReference" type="xs:string"/>
+    <xs:element name="EntityId1" type="xs:string"/>
+    <xs:element name="EntityId2" type="xs:string"/>
+    <xs:element name="EntityId3" type="xs:string"/>
+    <xs:element name="EntityId4" type="xs:string"/>
+    <xs:element name="EntityId5" type="xs:string"/>
+    <xs:element name="Terms">
+      <xs:complexType>
+        <xs:sequence>
+          <xs:element ref="pc:TermInfo" minOccurs="0" maxOccurs="unbounded"/>
+        </xs:sequence>
+      </xs:complexType>
+    </xs:element>
+    <xs:element name="TermInfo">
+      <xs:complexType>
+        <xs:sequence>
+          <xs:element ref="pc:TermName" minOccurs="0"/>
+          <xs:element ref="pc:TermId" minOccurs="0"/>
+        </xs:sequence>
+      </xs:complexType>
+    </xs:element>
+    <xs:element name="TermName" type="xs:string"/>
+    <xs:element name="TermId" type="xs:string"/>
+  </xs:schema>
+</ct:contentTypeSchema>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <TaxCatchAll xmlns="947c1918-d5ab-48a1-8b61-0d52f2f99fd1" xsi:nil="true"/>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="30973102-2308-455b-8e1f-b6a90edc3b23">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+  </documentManagement>
+</p:properties>
+</file>
+
+<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{74710830-637F-498E-B282-186C39A9FD81}"/>
+</file>
+
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{B19EEF9D-43D4-4CBD-9BF0-67E0A2471967}"/>
+</file>
+
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{F6F6DF86-2338-48FA-A47A-8663B0A9D366}"/>
 </file>